--- a/artfynd/A 23901-2026 artfynd.xlsx
+++ b/artfynd/A 23901-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112538720</v>
+        <v>112538724</v>
       </c>
       <c r="B2" t="n">
-        <v>89625</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582158</v>
+        <v>582098</v>
       </c>
       <c r="R2" t="n">
-        <v>6969902</v>
+        <v>6969669</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112538718</v>
+        <v>112538722</v>
       </c>
       <c r="B3" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582338</v>
+        <v>582131</v>
       </c>
       <c r="R3" t="n">
-        <v>6969635</v>
+        <v>6969798</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,16 +872,11 @@
         <v>112538723</v>
       </c>
       <c r="B4" t="n">
-        <v>90101</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -904,12 +889,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,7 +907,7 @@
         <v>581986</v>
       </c>
       <c r="R4" t="n">
-        <v>6969677</v>
+        <v>6969676</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112538722</v>
+        <v>112538719</v>
       </c>
       <c r="B5" t="n">
-        <v>89672</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582131</v>
+        <v>582240</v>
       </c>
       <c r="R5" t="n">
-        <v>6969799</v>
+        <v>6969822</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112538719</v>
+        <v>112538726</v>
       </c>
       <c r="B6" t="n">
-        <v>81483</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582240</v>
+        <v>582101</v>
       </c>
       <c r="R6" t="n">
-        <v>6969822</v>
+        <v>6969692</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112538729</v>
+        <v>112538720</v>
       </c>
       <c r="B7" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582131</v>
+        <v>582158</v>
       </c>
       <c r="R7" t="n">
-        <v>6969737</v>
+        <v>6969902</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112538724</v>
+        <v>112538729</v>
       </c>
       <c r="B8" t="n">
-        <v>89661</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582098</v>
+        <v>582130</v>
       </c>
       <c r="R8" t="n">
-        <v>6969669</v>
+        <v>6969738</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112538725</v>
+        <v>112538728</v>
       </c>
       <c r="B9" t="n">
-        <v>89679</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582105</v>
+        <v>582101</v>
       </c>
       <c r="R9" t="n">
-        <v>6969672</v>
+        <v>6969692</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112538728</v>
+        <v>112538721</v>
       </c>
       <c r="B10" t="n">
-        <v>73915</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582101</v>
+        <v>582117</v>
       </c>
       <c r="R10" t="n">
-        <v>6969692</v>
+        <v>6969836</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112538721</v>
+        <v>112538718</v>
       </c>
       <c r="B11" t="n">
-        <v>78809</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582117</v>
+        <v>582337</v>
       </c>
       <c r="R11" t="n">
-        <v>6969836</v>
+        <v>6969635</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,108 +1642,6 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>112538726</v>
-      </c>
-      <c r="B12" t="n">
-        <v>73935</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1467</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Rödbrun blekspik</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Sclerophora coniophaea</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Källmyrberget, Mpd</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>582101</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6969692</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Sundsvall</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Liden</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2023-10-04</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2023-10-04</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23901-2026 artfynd.xlsx
+++ b/artfynd/A 23901-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538724</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538722</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538723</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538719</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538726</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538720</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538729</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538728</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538721</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,8 +1692,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538718</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>